--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. TRES CANTOS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. TRES CANTOS.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>100.9961</v>
+        <v>112.3471</v>
       </c>
       <c r="E2" t="n">
-        <v>69.7407</v>
+        <v>80.0821</v>
       </c>
       <c r="F2" t="n">
-        <v>31.2553</v>
+        <v>32.2649</v>
       </c>
       <c r="G2" t="n">
         <v>75.069</v>
@@ -610,13 +610,13 @@
         <v>53.359</v>
       </c>
       <c r="S2" t="n">
-        <v>-8.123699999999999</v>
+        <v>3.2274</v>
       </c>
       <c r="T2" t="n">
-        <v>-8.7669</v>
+        <v>1.5745</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6434000000000001</v>
+        <v>1.653</v>
       </c>
       <c r="V2" t="n">
         <v>36.9611</v>
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>74.5286</v>
+        <v>68.36279999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>38.8478</v>
+        <v>36.3</v>
       </c>
       <c r="F3" t="n">
-        <v>35.6809</v>
+        <v>32.063</v>
       </c>
       <c r="G3" t="n">
         <v>30.2877</v>
@@ -688,13 +688,13 @@
         <v>57.4337</v>
       </c>
       <c r="S3" t="n">
-        <v>18.279</v>
+        <v>12.1132</v>
       </c>
       <c r="T3" t="n">
-        <v>10.1752</v>
+        <v>7.6272</v>
       </c>
       <c r="U3" t="n">
-        <v>8.104100000000001</v>
+        <v>4.4861</v>
       </c>
       <c r="V3" t="n">
         <v>5.0065</v>
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>48.0859</v>
+        <v>57.9179</v>
       </c>
       <c r="E4" t="n">
-        <v>21.8469</v>
+        <v>29.786</v>
       </c>
       <c r="F4" t="n">
-        <v>26.2391</v>
+        <v>28.1322</v>
       </c>
       <c r="G4" t="n">
         <v>32.955</v>
@@ -766,13 +766,13 @@
         <v>50.6423</v>
       </c>
       <c r="S4" t="n">
-        <v>-5.8366</v>
+        <v>3.9954</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.8825</v>
+        <v>4.0567</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.9541</v>
+        <v>-0.06099999999999994</v>
       </c>
       <c r="V4" t="n">
         <v>6.9971</v>
@@ -799,13 +799,13 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>43.0157</v>
+        <v>39.4927</v>
       </c>
       <c r="E5" t="n">
-        <v>30.1978</v>
+        <v>24.6208</v>
       </c>
       <c r="F5" t="n">
-        <v>12.8179</v>
+        <v>14.8718</v>
       </c>
       <c r="G5" t="n">
         <v>21.7341</v>
@@ -844,13 +844,13 @@
         <v>39.9705</v>
       </c>
       <c r="S5" t="n">
-        <v>12.4298</v>
+        <v>8.9064</v>
       </c>
       <c r="T5" t="n">
-        <v>13.0142</v>
+        <v>7.4374</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5843999999999999</v>
+        <v>1.4691</v>
       </c>
       <c r="V5" t="n">
         <v>-9.9688</v>
@@ -877,13 +877,13 @@
         <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>32.4256</v>
+        <v>25.0214</v>
       </c>
       <c r="E6" t="n">
-        <v>23.9666</v>
+        <v>16.5087</v>
       </c>
       <c r="F6" t="n">
-        <v>8.4588</v>
+        <v>8.512700000000001</v>
       </c>
       <c r="G6" t="n">
         <v>24.287</v>
@@ -922,13 +922,13 @@
         <v>37.2546</v>
       </c>
       <c r="S6" t="n">
-        <v>15.4964</v>
+        <v>8.0923</v>
       </c>
       <c r="T6" t="n">
-        <v>15.7385</v>
+        <v>8.2807</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2421000000000002</v>
+        <v>-0.1884</v>
       </c>
       <c r="V6" t="n">
         <v>-12.5964</v>
@@ -955,13 +955,13 @@
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>22.7428</v>
+        <v>24.1796</v>
       </c>
       <c r="E7" t="n">
-        <v>3.398600000000001</v>
+        <v>3.825200000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>19.344</v>
+        <v>20.3542</v>
       </c>
       <c r="G7" t="n">
         <v>-7.5205</v>
@@ -1000,13 +1000,13 @@
         <v>35.1202</v>
       </c>
       <c r="S7" t="n">
-        <v>4.482500000000001</v>
+        <v>5.9196</v>
       </c>
       <c r="T7" t="n">
-        <v>3.9675</v>
+        <v>4.3942</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5148</v>
+        <v>1.5251</v>
       </c>
       <c r="V7" t="n">
         <v>15.1092</v>
@@ -1033,13 +1033,13 @@
         <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>17.3213</v>
+        <v>13.1569</v>
       </c>
       <c r="E8" t="n">
-        <v>8.713900000000001</v>
+        <v>4.5175</v>
       </c>
       <c r="F8" t="n">
-        <v>8.6075</v>
+        <v>8.6395</v>
       </c>
       <c r="G8" t="n">
         <v>16.4838</v>
@@ -1078,13 +1078,13 @@
         <v>33.5678</v>
       </c>
       <c r="S8" t="n">
-        <v>5.3246</v>
+        <v>1.1599</v>
       </c>
       <c r="T8" t="n">
-        <v>5.827</v>
+        <v>1.6305</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5028000000000002</v>
+        <v>-0.4707</v>
       </c>
       <c r="V8" t="n">
         <v>-8.9497</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>R. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>7.144899999999999</v>
+        <v>11.4877</v>
       </c>
       <c r="E9" t="n">
-        <v>3.8506</v>
+        <v>1.3792</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2943</v>
+        <v>10.1083</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3063000000000002</v>
+        <v>10.9741</v>
       </c>
       <c r="H9" t="n">
-        <v>1.113</v>
+        <v>6.707</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8065</v>
+        <v>4.2671</v>
       </c>
       <c r="J9" t="n">
-        <v>4.229</v>
+        <v>14.6445</v>
       </c>
       <c r="K9" t="n">
-        <v>5.5078</v>
+        <v>11.2501</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2787</v>
+        <v>3.3944</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.922099999999999</v>
+        <v>-3.6703</v>
       </c>
       <c r="N9" t="n">
-        <v>-4.3944</v>
+        <v>-4.542999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4723999999999999</v>
+        <v>0.8727</v>
       </c>
       <c r="P9" t="n">
-        <v>18.2391</v>
+        <v>6.015</v>
       </c>
       <c r="Q9" t="n">
-        <v>-7.1792</v>
+        <v>-18.6272</v>
       </c>
       <c r="R9" t="n">
-        <v>25.4184</v>
+        <v>24.642</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3533</v>
+        <v>2.0205</v>
       </c>
       <c r="T9" t="n">
-        <v>3.4161</v>
+        <v>2.0244</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.0626</v>
+        <v>-0.004199999999999995</v>
       </c>
       <c r="V9" t="n">
-        <v>-12.754</v>
+        <v>-7.521999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>3.3851</v>
+        <v>3.3373</v>
       </c>
       <c r="X9" t="n">
-        <v>-16.1393</v>
+        <v>-10.8595</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. LARDIES GUILLEN</t>
+          <t>J. DOMINGUEZ LARRE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>3.538400000000001</v>
+        <v>10.0241</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8916</v>
+        <v>-3.2764</v>
       </c>
       <c r="F10" t="n">
-        <v>7.430000000000001</v>
+        <v>13.3005</v>
       </c>
       <c r="G10" t="n">
-        <v>10.9741</v>
+        <v>1.072599999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>6.707</v>
+        <v>2.9262</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2671</v>
+        <v>-1.853600000000002</v>
       </c>
       <c r="J10" t="n">
-        <v>14.6445</v>
+        <v>14.4781</v>
       </c>
       <c r="K10" t="n">
-        <v>11.2501</v>
+        <v>11.3038</v>
       </c>
       <c r="L10" t="n">
-        <v>3.3944</v>
+        <v>3.1742</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.6703</v>
+        <v>-13.4057</v>
       </c>
       <c r="N10" t="n">
-        <v>-4.542999999999999</v>
+        <v>-8.377599999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8727</v>
+        <v>-5.0278</v>
       </c>
       <c r="P10" t="n">
-        <v>6.015</v>
+        <v>12.806</v>
       </c>
       <c r="Q10" t="n">
-        <v>-18.6272</v>
+        <v>-33.7617</v>
       </c>
       <c r="R10" t="n">
-        <v>24.642</v>
+        <v>46.5679</v>
       </c>
       <c r="S10" t="n">
-        <v>-5.9288</v>
+        <v>0.1111</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.2464</v>
+        <v>1.7938</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.6829</v>
+        <v>-1.6829</v>
       </c>
       <c r="V10" t="n">
-        <v>-7.521999999999999</v>
+        <v>-3.9658</v>
       </c>
       <c r="W10" t="n">
-        <v>3.3373</v>
+        <v>14.2132</v>
       </c>
       <c r="X10" t="n">
-        <v>-10.8595</v>
+        <v>-18.1789</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. JIMENO GONZALEZ</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1715999999999998</v>
+        <v>6.1646</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6973</v>
+        <v>2.3753</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5258</v>
+        <v>3.789099999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5358999999999998</v>
+        <v>0.3063000000000002</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1356</v>
+        <v>1.113</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.6715</v>
+        <v>-0.8065</v>
       </c>
       <c r="J11" t="n">
-        <v>3.327999999999999</v>
+        <v>4.229</v>
       </c>
       <c r="K11" t="n">
-        <v>4.391299999999999</v>
+        <v>5.5078</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.0632</v>
+        <v>-1.2787</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.8639</v>
+        <v>-3.922099999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2556</v>
+        <v>-4.3944</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.6082</v>
+        <v>0.4723999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3582</v>
+        <v>18.2391</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.1046</v>
+        <v>-7.1792</v>
       </c>
       <c r="R11" t="n">
-        <v>4.4627</v>
+        <v>25.4184</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.1168</v>
+        <v>0.3735999999999998</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.9383</v>
+        <v>1.9406</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1789</v>
+        <v>-1.5671</v>
       </c>
       <c r="V11" t="n">
-        <v>2.4659</v>
+        <v>-12.754</v>
       </c>
       <c r="W11" t="n">
-        <v>5.4119</v>
+        <v>3.3851</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.9459</v>
+        <v>-16.1393</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. GOMEZ DE ENTERRIA LOPEZ</t>
+          <t>F. JIMENO GONZALEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02719999999999967</v>
+        <v>1.8178</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2541</v>
+        <v>4.7984</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2812</v>
+        <v>-2.9808</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1025</v>
+        <v>-0.5358999999999998</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.849</v>
+        <v>3.1356</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7464</v>
+        <v>-3.6715</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8967</v>
+        <v>3.327999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2224</v>
+        <v>4.391299999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>1.6743</v>
+        <v>-1.0632</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.9992</v>
+        <v>-3.8639</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.0715</v>
+        <v>-1.2556</v>
       </c>
       <c r="O12" t="n">
-        <v>0.07219999999999999</v>
+        <v>-2.6082</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7761999999999999</v>
+        <v>1.3582</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.433</v>
+        <v>-3.1046</v>
       </c>
       <c r="R12" t="n">
-        <v>6.209099999999999</v>
+        <v>4.4627</v>
       </c>
       <c r="S12" t="n">
-        <v>2.0028</v>
+        <v>-1.4706</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4253</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5773</v>
+        <v>-0.6336999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.6493</v>
+        <v>2.4659</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.1433</v>
+        <v>5.4119</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.506</v>
+        <v>-2.9459</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. GOMEZ GONZALEZ</t>
+          <t>F. GOMEZ DE ENTERRIA LOPEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.0848</v>
+        <v>-0.1825999999999997</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0069</v>
+        <v>-2.572899999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9222</v>
+        <v>2.3902</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.5933</v>
+        <v>-1.1025</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3287</v>
+        <v>-2.849</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.2646</v>
+        <v>1.7464</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.5706</v>
+        <v>1.8967</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3172</v>
+        <v>0.2224</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2535</v>
+        <v>1.6743</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.02270000000000003</v>
+        <v>-2.9992</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0115</v>
+        <v>-3.0715</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0111</v>
+        <v>0.07219999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>0.388</v>
+        <v>0.7761999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.194</v>
+        <v>-5.433</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5821000000000001</v>
+        <v>6.209099999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1205</v>
+        <v>1.7931</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2422</v>
+        <v>1.1065</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3627</v>
+        <v>0.6865</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-1.6493</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.1433</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. ROCA GARCIA</t>
+          <t>A. GOMEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.34</v>
+        <v>-1.2028</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.1044</v>
+        <v>-1.9068</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7644</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.8751</v>
+        <v>-1.5933</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3024000000000001</v>
+        <v>-0.3287</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.5727</v>
+        <v>-1.2646</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.8141</v>
+        <v>-1.5706</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.1904</v>
+        <v>-0.3172</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.6237</v>
+        <v>-1.2535</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9392</v>
+        <v>-0.02270000000000003</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8882000000000001</v>
+        <v>-0.0115</v>
       </c>
       <c r="O14" t="n">
-        <v>1.051</v>
+        <v>-0.0111</v>
       </c>
       <c r="P14" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.194</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.5821000000000001</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.002500000000000002</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.1421</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.1446</v>
+      </c>
+      <c r="V14" t="n">
         <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-1.9404</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.9403</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-1.1828</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-0.8329</v>
-      </c>
-      <c r="V14" t="n">
-        <v>-0.2821</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ LARRE</t>
+          <t>M. ROCA GARCIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.2667</v>
+        <v>-2.2668</v>
       </c>
       <c r="E15" t="n">
-        <v>-12.2531</v>
+        <v>-5.222</v>
       </c>
       <c r="F15" t="n">
-        <v>6.986499999999999</v>
+        <v>2.9553</v>
       </c>
       <c r="G15" t="n">
-        <v>1.072599999999999</v>
+        <v>-1.8751</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9262</v>
+        <v>-0.3024000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.853600000000002</v>
+        <v>-1.5727</v>
       </c>
       <c r="J15" t="n">
-        <v>14.4781</v>
+        <v>-3.8141</v>
       </c>
       <c r="K15" t="n">
-        <v>11.3038</v>
+        <v>-1.1904</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1742</v>
+        <v>-2.6237</v>
       </c>
       <c r="M15" t="n">
-        <v>-13.4057</v>
+        <v>1.9392</v>
       </c>
       <c r="N15" t="n">
-        <v>-8.377599999999999</v>
+        <v>0.8882000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-5.0278</v>
+        <v>1.051</v>
       </c>
       <c r="P15" t="n">
-        <v>12.806</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-33.7617</v>
+        <v>-1.9404</v>
       </c>
       <c r="R15" t="n">
-        <v>46.5679</v>
+        <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>-15.1796</v>
+        <v>-0.1096999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-7.1832</v>
+        <v>0.5324</v>
       </c>
       <c r="U15" t="n">
-        <v>-7.9969</v>
+        <v>-0.6421</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.9658</v>
+        <v>-0.2821</v>
       </c>
       <c r="W15" t="n">
-        <v>14.2132</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-18.1789</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>-8.7646</v>
+        <v>-5.8489</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.554</v>
+        <v>-4.8892</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2107</v>
+        <v>-0.9596999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>-0.5443000000000002</v>
@@ -1702,13 +1702,13 @@
         <v>8.5375</v>
       </c>
       <c r="S16" t="n">
-        <v>-5.6323</v>
+        <v>-2.7167</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.7891</v>
+        <v>-0.1244</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.8433</v>
+        <v>-2.5923</v>
       </c>
       <c r="V16" t="n">
         <v>-4.1403</v>
@@ -1735,13 +1735,13 @@
         <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>-21.995</v>
+        <v>-20.4905</v>
       </c>
       <c r="E17" t="n">
-        <v>-31.5375</v>
+        <v>-34.2512</v>
       </c>
       <c r="F17" t="n">
-        <v>9.5426</v>
+        <v>13.7605</v>
       </c>
       <c r="G17" t="n">
         <v>-14.6617</v>
@@ -1780,13 +1780,13 @@
         <v>38.0304</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1033</v>
+        <v>4.6078</v>
       </c>
       <c r="T17" t="n">
-        <v>7.5531</v>
+        <v>4.839399999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-4.45</v>
+        <v>-0.2317000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>-12.5708</v>
@@ -1813,13 +1813,13 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>309.547</v>
+        <v>339.981</v>
       </c>
       <c r="E18" t="n">
-        <v>139.6586</v>
+        <v>152.0747</v>
       </c>
       <c r="F18" t="n">
-        <v>169.8882</v>
+        <v>187.9058</v>
       </c>
       <c r="G18" t="n">
         <v>185.3363</v>
@@ -1858,16 +1858,16 @@
         <v>463.7385</v>
       </c>
       <c r="S18" t="n">
-        <v>17.5916</v>
+        <v>48.0258</v>
       </c>
       <c r="T18" t="n">
-        <v>33.7183</v>
+        <v>46.1346</v>
       </c>
       <c r="U18" t="n">
-        <v>-16.1286</v>
+        <v>1.8903</v>
       </c>
       <c r="V18" t="n">
-        <v>-7.859400000000001</v>
+        <v>-7.859400000000004</v>
       </c>
       <c r="W18" t="n">
         <v>176.5781</v>
